--- a/data/trans_dic/P15D$nada-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P15D$nada-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tuvo consecuencias el último accidente</t>
+          <t>Población que no tuvo consecuencias el último accidente (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,3; 38,87</t>
+          <t>4,39; 36,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,64; 30,65</t>
+          <t>10,6; 28,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,79; 27,62</t>
+          <t>7,73; 29,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,25; 44,25</t>
+          <t>18,44; 44,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,01; 26,51</t>
+          <t>6,09; 26,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,15; 37,75</t>
+          <t>21,21; 38,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,37; 28,12</t>
+          <t>10,19; 29,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,79; 29,24</t>
+          <t>16,05; 28,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,0; 24,88</t>
+          <t>8,06; 25,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,77; 31,79</t>
+          <t>19,25; 31,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,43; 25,6</t>
+          <t>11,22; 25,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,45; 30,68</t>
+          <t>17,84; 30,75</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,43; 36,23</t>
+          <t>15,84; 36,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,98; 32,45</t>
+          <t>19,99; 32,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,47; 26,21</t>
+          <t>11,42; 25,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 16,81</t>
+          <t>6,48; 18,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,38; 34,81</t>
+          <t>7,22; 32,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,91; 38,8</t>
+          <t>21,06; 38,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,54; 21,13</t>
+          <t>5,9; 20,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,0; 26,78</t>
+          <t>12,24; 27,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,67; 32,77</t>
+          <t>15,93; 32,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,32; 33,0</t>
+          <t>22,25; 33,86</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,1; 21,27</t>
+          <t>10,77; 21,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,98; 18,72</t>
+          <t>9,61; 18,76</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,39; 67,0</t>
+          <t>20,93; 68,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,76; 55,37</t>
+          <t>18,45; 55,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 28,71</t>
+          <t>2,64; 29,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,22; 47,67</t>
+          <t>7,73; 48,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,62; 54,93</t>
+          <t>2,31; 50,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,01; 35,12</t>
+          <t>7,27; 37,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 27,22</t>
+          <t>3,02; 26,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,55; 29,72</t>
+          <t>8,75; 28,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,84; 53,73</t>
+          <t>18,1; 51,45</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,74; 39,47</t>
+          <t>13,84; 39,82</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,66; 21,62</t>
+          <t>5,04; 22,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,08; 34,97</t>
+          <t>10,9; 35,25</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,7; 36,19</t>
+          <t>18,6; 34,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,71; 30,31</t>
+          <t>19,85; 30,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,38; 22,27</t>
+          <t>11,29; 22,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,85; 21,79</t>
+          <t>11,09; 21,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,23; 24,85</t>
+          <t>9,93; 25,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,3; 34,01</t>
+          <t>22,37; 34,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,28; 20,55</t>
+          <t>9,48; 20,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,86; 24,08</t>
+          <t>14,44; 23,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,24; 28,3</t>
+          <t>16,9; 28,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,95; 30,69</t>
+          <t>23,02; 30,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,69; 19,54</t>
+          <t>11,87; 19,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,39; 21,66</t>
+          <t>14,37; 21,7</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tuvo consecuencias el último accidente</t>
+          <t>Población que no tuvo consecuencias el último accidente (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1082; 9786</t>
+          <t>1106; 9229</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8704; 22930</t>
+          <t>7932; 21411</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3560; 12624</t>
+          <t>3532; 13377</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6142; 15756</t>
+          <t>6567; 15724</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2736; 12070</t>
+          <t>2774; 12257</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22537; 42227</t>
+          <t>23724; 43030</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6993; 20976</t>
+          <t>7605; 21829</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12564; 23261</t>
+          <t>12770; 22811</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5660; 17592</t>
+          <t>5699; 17923</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35042; 59349</t>
+          <t>35941; 58507</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13756; 30802</t>
+          <t>13501; 30534</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21249; 35326</t>
+          <t>20544; 35408</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13680; 28440</t>
+          <t>12431; 29024</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36370; 59066</t>
+          <t>36379; 58386</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13902; 31759</t>
+          <t>13833; 31353</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8045; 21856</t>
+          <t>8423; 23974</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2588; 12197</t>
+          <t>2531; 11297</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24909; 44114</t>
+          <t>23943; 44266</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5537; 17887</t>
+          <t>4997; 17716</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12233; 27308</t>
+          <t>12479; 28266</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17796; 37210</t>
+          <t>18085; 36452</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66001; 97592</t>
+          <t>65808; 100132</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22838; 43788</t>
+          <t>22168; 44645</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23159; 43422</t>
+          <t>22304; 43513</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3762; 12997</t>
+          <t>4060; 13345</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4105; 14425</t>
+          <t>4806; 14511</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>792; 8842</t>
+          <t>812; 9157</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2732; 15838</t>
+          <t>2567; 16275</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>877; 7271</t>
+          <t>306; 6727</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2017; 10106</t>
+          <t>2091; 10871</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>990; 8440</t>
+          <t>938; 8072</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2638; 9173</t>
+          <t>2700; 8822</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6148; 17535</t>
+          <t>5908; 16790</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8632; 21640</t>
+          <t>7586; 21833</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2878; 13359</t>
+          <t>3113; 14162</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7102; 22411</t>
+          <t>6987; 22592</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24250; 44542</t>
+          <t>22894; 42545</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>55746; 85740</t>
+          <t>56149; 86534</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22486; 44024</t>
+          <t>22308; 43806</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21570; 43335</t>
+          <t>22059; 43402</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9594; 23310</t>
+          <t>9318; 23607</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>56707; 86513</t>
+          <t>56893; 87597</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17651; 39101</t>
+          <t>18046; 38099</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31557; 51131</t>
+          <t>30663; 50479</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>37386; 61372</t>
+          <t>36652; 60982</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>123277; 164859</t>
+          <t>123666; 164036</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45364; 75809</t>
+          <t>46040; 75327</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>59169; 89093</t>
+          <t>59082; 89229</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15D$nada-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P15D$nada-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,39; 36,66</t>
+          <t>4,53; 37,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,6; 28,62</t>
+          <t>10,9; 29,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,73; 29,27</t>
+          <t>7,59; 28,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,44; 44,16</t>
+          <t>18,22; 42,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,09; 26,92</t>
+          <t>5,82; 24,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,21; 38,47</t>
+          <t>21,29; 37,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,19; 29,26</t>
+          <t>10,1; 29,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,05; 28,67</t>
+          <t>14,73; 27,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,06; 25,35</t>
+          <t>8,01; 24,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,25; 31,34</t>
+          <t>19,36; 31,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,22; 25,38</t>
+          <t>11,01; 25,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,84; 30,75</t>
+          <t>18,11; 30,05</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,84; 36,97</t>
+          <t>17,18; 36,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,99; 32,08</t>
+          <t>19,65; 32,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,42; 25,87</t>
+          <t>11,17; 26,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,48; 18,44</t>
+          <t>5,57; 15,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,22; 32,24</t>
+          <t>8,06; 35,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,06; 38,93</t>
+          <t>20,92; 39,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,9; 20,93</t>
+          <t>6,54; 21,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,24; 27,72</t>
+          <t>10,87; 25,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,93; 32,1</t>
+          <t>16,38; 32,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,25; 33,86</t>
+          <t>22,14; 33,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,77; 21,69</t>
+          <t>10,62; 21,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,61; 18,76</t>
+          <t>9,32; 17,48</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,93; 68,79</t>
+          <t>16,14; 67,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,45; 55,7</t>
+          <t>18,13; 57,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 29,74</t>
+          <t>2,49; 33,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 48,98</t>
+          <t>7,16; 40,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 50,82</t>
+          <t>6,71; 53,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,27; 37,78</t>
+          <t>6,59; 37,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 26,03</t>
+          <t>3,09; 24,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,75; 28,58</t>
+          <t>7,86; 27,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,1; 51,45</t>
+          <t>18,5; 53,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,84; 39,82</t>
+          <t>14,42; 40,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,04; 22,91</t>
+          <t>4,37; 20,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,9; 35,25</t>
+          <t>10,3; 30,59</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,6; 34,57</t>
+          <t>18,72; 34,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,85; 30,59</t>
+          <t>19,96; 30,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,29; 22,16</t>
+          <t>11,94; 22,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,09; 21,82</t>
+          <t>10,37; 20,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,93; 25,17</t>
+          <t>10,6; 25,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,37; 34,44</t>
+          <t>22,94; 34,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,48; 20,02</t>
+          <t>9,54; 19,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,44; 23,77</t>
+          <t>14,19; 23,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,9; 28,12</t>
+          <t>16,71; 28,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,02; 30,53</t>
+          <t>23,02; 30,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,87; 19,42</t>
+          <t>12,02; 19,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,37; 21,7</t>
+          <t>13,42; 20,24</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10409</t>
+          <t>10927</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17285</t>
+          <t>17693</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27693</t>
+          <t>28620</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1106; 9229</t>
+          <t>1140; 9555</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7932; 21411</t>
+          <t>8155; 21846</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3532; 13377</t>
+          <t>3468; 12801</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6567; 15724</t>
+          <t>6895; 16051</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2774; 12257</t>
+          <t>2649; 11318</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23724; 43030</t>
+          <t>23811; 42277</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7605; 21829</t>
+          <t>7537; 22083</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12770; 22811</t>
+          <t>12446; 23333</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5699; 17923</t>
+          <t>5664; 17551</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35941; 58507</t>
+          <t>36143; 59516</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13501; 30534</t>
+          <t>13249; 30243</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20544; 35408</t>
+          <t>22162; 36772</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13636</t>
+          <t>13448</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18489</t>
+          <t>19167</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32126</t>
+          <t>32615</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12431; 29024</t>
+          <t>13488; 28953</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36379; 58386</t>
+          <t>35770; 59994</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13833; 31353</t>
+          <t>13535; 31898</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8423; 23974</t>
+          <t>7809; 21911</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2531; 11297</t>
+          <t>2826; 12289</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23943; 44266</t>
+          <t>23784; 44461</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4997; 17716</t>
+          <t>5540; 18121</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12479; 28266</t>
+          <t>12073; 28032</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18085; 36452</t>
+          <t>18598; 37070</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65808; 100132</t>
+          <t>65485; 98374</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22168; 44645</t>
+          <t>21856; 43799</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22304; 43513</t>
+          <t>23407; 43912</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5372</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13065</t>
+          <t>13565</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4060; 13345</t>
+          <t>3132; 13114</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4806; 14511</t>
+          <t>4724; 15007</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>812; 9157</t>
+          <t>768; 10230</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2567; 16275</t>
+          <t>2986; 17060</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>306; 6727</t>
+          <t>888; 7051</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2091; 10871</t>
+          <t>1895; 10671</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>938; 8072</t>
+          <t>959; 7636</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2700; 8822</t>
+          <t>2770; 9748</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5908; 16790</t>
+          <t>6037; 17477</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7586; 21833</t>
+          <t>7905; 22237</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3113; 14162</t>
+          <t>2700; 12392</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6987; 22592</t>
+          <t>7919; 23526</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31885</t>
+          <t>32567</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>40998</t>
+          <t>42232</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72884</t>
+          <t>74799</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22894; 42545</t>
+          <t>23046; 42555</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>56149; 86534</t>
+          <t>56452; 86790</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22308; 43806</t>
+          <t>23606; 45093</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22059; 43402</t>
+          <t>22793; 45812</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9318; 23607</t>
+          <t>9943; 24120</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>56893; 87597</t>
+          <t>58345; 87992</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18046; 38099</t>
+          <t>18150; 37960</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30663; 50479</t>
+          <t>32745; 54038</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36652; 60982</t>
+          <t>36241; 61094</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>123666; 164036</t>
+          <t>123650; 164775</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>46040; 75327</t>
+          <t>46624; 75440</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>59082; 89229</t>
+          <t>60438; 91184</t>
         </is>
       </c>
     </row>
